--- a/www/download/COUNTRY.KOR.EXI382.xlsx
+++ b/www/download/COUNTRY.KOR.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>Coreia do Sul</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29914478527607</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29941042944785</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29941042944785</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29941042944785</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29941042944785</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29941042944785</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29941042944785</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29941042944785</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29941042944785</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.29941042944785</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>37.777</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>20.47</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>20.857</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>21.151</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>20.02</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>20.308</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>21.184</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>21.601</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>22.191</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>22.174</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>22.587</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>22.885</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>23.188</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>23.348</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>23.679</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>23.493</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>23.816</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>24.232</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>24.671</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>23.426</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>28.325</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>33.323</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>33.152</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>34.129</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>34.174</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>34.307</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>34.274</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>27.465</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>12.813</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>13.099</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>13.266</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>12.211</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>12.547</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>13.382</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>13.682</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>14.199</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>14.431</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>14.917</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>15.207</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>15.581</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>16.015</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>16.247</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>16.441</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>16.957</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>17.384</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>17.703</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>16.978</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>24.037</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>24.112</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>24.771</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>24.899</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>24.866</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>24.905</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>89129.146</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>48765.4</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>49780.583</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50512.35</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>47655.703</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>48447.263</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50678.971</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>51745.589</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>53168.73</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>53038.633</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>54153.754</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>54841.327</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>55521.003</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>55830.457</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>56633.551</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>56065.176</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>55898.407</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>56933.777</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>57958.028</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>55088.013</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>66462.233</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>78217.401</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>77777.735</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>80198.855</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>80376.95</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>80575.582</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>80601.278</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>63979.516</t>
+          <t>144518546457.536</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12546.9</t>
+          <t>72874353958.4666</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12965.635</t>
+          <t>78832686723.8581</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13031.732</t>
+          <t>67001278751.9562</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10644.773</t>
+          <t>71282475230.1916</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11519.299</t>
+          <t>81019303300.3362</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13495.613</t>
+          <t>80936699368.7913</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13935.695</t>
+          <t>85679841447.1374</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14930.33</t>
+          <t>78927607259.6444</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15963.491</t>
+          <t>98986981085.1174</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>17258.712</t>
+          <t>102699746351.382</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>17932.969</t>
+          <t>102496229426.36</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>18992.347</t>
+          <t>96764012455.6199</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20735.217</t>
+          <t>108637692092.272</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>21009.087</t>
+          <t>96190695280.7865</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>22212.254</t>
+          <t>99034594527.6925</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>23517.883</t>
+          <t>111722961618.011</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>24545.701</t>
+          <t>106656436556.623</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>24995.408</t>
+          <t>111911100469.852</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>39652.84</t>
+          <t>108656884469.26</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>47984.688</t>
+          <t>122514652870.166</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>55827.931</t>
+          <t>134584205315.303</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>55856.191</t>
+          <t>142960429044.673</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>57382.663</t>
+          <t>154441924778.276</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>57759.799</t>
+          <t>150583898845.341</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>57516.397</t>
+          <t>157364988204.135</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>57720.477</t>
+          <t>165672530394.769</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>44064772336.5896</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>22954195897.4961</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>23546813635.3446</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>18236858597.4496</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>19492063554.0828</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>21237471245.3093</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>22222494262.9665</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22839094915.6499</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>23547670309.3092</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>25957193304.7733</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>26040197509.7438</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>30064875269.8189</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>23289278770.7896</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>25426841804.1308</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>23219321925.8053</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>22288161624.081</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>22852926204.2908</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>26294982997.7901</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>26612280782.9287</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>24294639759.4208</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>19278957104.1643</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>24860726924.9939</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>26330170027.8482</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22496942182.9539</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>24654174745.6673</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>24285926091.5296</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>24247427125.9333</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>46624149.1331378</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>23312742.1033055</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>24559494.191046</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>28026158.6919312</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>14785226.5673917</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10430155.5705037</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10966508.5225905</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9671202.12089258</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>10311433.5914331</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>9994608.98979532</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>9322717.14374197</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>9479704.00817908</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>7302116.38387291</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>8895194.9988118</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>9364742.33179021</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>6758996.64522161</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>7012405.96666312</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>5789318.6235281</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6379994.72466467</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>7287408.55813484</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>6920499.8685387</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8403233.67941226</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>8067447.18790096</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8415906.70823921</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>8192452.63143096</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>8271656.21599866</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>7295640.97736211</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>174097.660814194</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>209080.245905868</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>227045.941812167</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>232051.332921064</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>224609.583322174</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>266908.428966457</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>285211.980370599</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>279016.60091411</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>264229.049667442</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>258943.967255994</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>281540.350306148</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>302967.660275207</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>316944.88695509</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>318200.552474306</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>326922.355542666</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>370245.988275054</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>392198.271019119</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>438993.36984693</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>434234.975444001</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>443149.088286452</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>546947.779828069</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>601993.047812866</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>635504.663168633</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>655963.195157108</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>694981.852582076</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>661834.416467527</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>645310.663722735</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>538707.715526128</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>553777.493992695</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>652468.508409186</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>570109.929223995</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>639781.232579108</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>869240.992538326</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>871910.948077003</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>894723.457573979</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>757135.294805184</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>927945.712260615</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1032109.01234551</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1101866.23005829</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1077749.06994524</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1215819.76622403</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1078792.98981328</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1280850.03733301</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1504272.67528791</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1585058.53909825</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1624611.12323473</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1632704.29742394</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2079581.74448986</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2082211.15741883</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2338416.6970943</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2456932.36351385</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2552377.62040623</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2537424.98863883</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2622705.52672176</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.451942497506151</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.453394052397765</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.449367748826139</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.28541793915062</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.453891940662304</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.457595545771201</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.392704849405332</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.389831556309615</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.365952987965394</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.385007045539498</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.337228068506893</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.403524250839091</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.184502569318384</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.184514649530017</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.0951894690498749</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.0034057373298243</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.0290972276267116</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.066525313895038</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.0607566407446695</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.632164157332281</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.48896701795086</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.24562747411909</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.12137602599159</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.55068724301167</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.34279994868492</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.36830155796635</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.38047842065593</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1604.40110525052</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1791.51903170289</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1797.60391139371</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1374.69630090662</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1596.33623144683</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1692.5794383949</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1660.5637409283</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1669.34144031281</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1658.34503393144</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1798.72310838285</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1745.73107027366</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1976.98983848762</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1494.70379500852</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1587.73872453899</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1429.11000688151</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1355.63688707504</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1347.68276627577</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1512.57941106243</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1503.29786488648</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1430.91445756961</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>934.036399494779</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1034.27654026799</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1092.00114871422</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>908.182193956516</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>990.175795491176</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>976.676704196851</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>973.592348408537</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>31557926766.7316</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>12907857343.8143</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>17031078403.9553</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>14765097807.3183</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>18397212503.4678</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>20143879973.3594</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>21035599933.579</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>23035011620.8067</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>20309382655.8452</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>29182284839.8008</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>28406852077.7617</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>27106639597.5516</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>22200918447.5731</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>22193588668.4295</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>22408400528.8231</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>24880599316.0949</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>24531598623.381</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>26794584988.4347</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>31047111516.6053</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>29129091490.9799</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>31492334372.5757</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>33355353901.1906</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>33304592776.5564</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>35599977277.4183</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>31786702483.8169</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>35454335023.1647</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>37344499258.7542</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>45383258104.0689</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>16920966024.7628</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>21031567643.3565</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>17978740868.1634</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>22083563346.7919</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>24491689311.7515</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>24878525258.1308</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>27748417781.1006</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>24513845097.1882</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>34397879373.1797</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>34742892720.3065</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>32346690264.7539</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>26269174661.1478</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>26643575475.1674</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>26726300117.8579</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>29848829025.1567</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>29419023714.5159</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>31822315004.3288</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>36179868099.8523</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>33678750615.0336</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>36204673408.0288</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>38505113518.3159</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>34894804138.1224</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>37338336404.2515</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>33409459391.1192</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>37274816703.0814</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>40297382007.2896</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-13825331337.3373</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-4013108680.94854</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-4000489239.40119</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-3213643060.8451</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-3686350843.32405</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-4347809338.3921</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-3842925324.55183</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-4713406160.29389</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-4204462441.34299</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-5215594533.37886</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-6336040642.54478</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-5240050667.20227</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-4068256213.57475</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-4449986806.73793</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-4317899589.03484</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-4968229709.0618</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-4887425091.13498</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-5027730015.89414</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-5132756583.247</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-4549659124.05372</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-4712339035.45312</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-5149759617.1253</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-1590211361.56596</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-1738359126.83321</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-1622756907.30222</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-1820481679.91673</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-2952882748.53547</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>2329.49814775907</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>979.254957971395</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>989.818688449658</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>982.333315743874</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>871.772081405879</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>918.062626521474</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>1008.4523071191</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1018.57946862353</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.306</t>
+          <t>1051.46871368665</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>1106.20203868075</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.707</t>
+          <t>1157.0215533128</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1179.22649499541</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.013</t>
+          <t>1218.92710445951</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1294.77767023544</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>1293.07378411259</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>1351.01994392305</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2.323</t>
+          <t>1386.89659849469</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2.543</t>
+          <t>1411.95459095033</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.535</t>
+          <t>1411.96253657734</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2.961</t>
+          <t>2335.48728985367</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>3.536</t>
+          <t>2324.78579190808</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>3.553</t>
+          <t>2322.59981466265</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>3.795</t>
+          <t>2316.54505723763</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3.861</t>
+          <t>2316.48873645523</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>3.847</t>
+          <t>2319.78380286578</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>3.925</t>
+          <t>2313.06496017884</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>4.151</t>
+          <t>2317.61557590226</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>2359.33896170336</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>2382.22808431647</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>2386.71085561938</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>2388.20044631895</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>2380.42852575998</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>2385.63627947749</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>2392.32302681381</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>2395.57366727539</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>2395.95917263832</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>2391.92897086656</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>2397.56293443054</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>2396.36651635105</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>2394.36450436012</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>2391.18984598456</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>2391.75085625462</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>2386.45287339803</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>2347.13410537656</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>2349.56738308676</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>2349.19899154592</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>2351.56133487041</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>2346.38218160008</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>2347.26214983196</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>2346.06315100345</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>2349.87416410358</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>2351.98596472562</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>2348.68992421357</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>2351.66733239607</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>128667.20984757</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>134945.45680249</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>166144.157963375</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>161916.501695062</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>179868.111670175</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>252930.594936933</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>232995.549835213</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>234383.516050256</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>228022.913577834</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>274240.05612547</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>310815.079596157</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>345275.217577567</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>365110.376523045</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>381467.188101201</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>351498.095780546</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>472094.502937559</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>562864.272307852</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>638844.744197439</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>624468.742744575</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>628225.674941011</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>672463.607374378</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>644131.723047806</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>703073.53264646</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>730926.099269956</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>702949.53067841</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>727888.055798029</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>754474.623998642</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20568801013.6021</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>9726389209.79237</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>11437667382.6082</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>13101577601.3363</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>11998227717.7849</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>13951752965.7275</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>13497623356.7542</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>14170668368.5144</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>13419208264.9715</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>18175526521.281</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>18049471699.718</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>18520082429.637</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>17634829368.4186</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>22297904442.3304</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>20981191239.6444</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>21110415683.2042</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>26782916374.3403</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>25933188808.1668</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>27118242787.7472</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>24676081612.5105</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>24837514471.1798</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>27230081366.6901</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>28532396428.1721</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>31314483561.1117</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>29772630487.1963</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>31813617992.4145</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>32285553198.1066</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>134424.64660383</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>154114.606866331</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>171613.780438255</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>114651.424237013</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>146821.634268951</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>238391.335618737</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>222196.140843919</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>224049.87320437</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>214866.688923225</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>245114.028773453</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>288768.729311375</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>338681.331045353</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>354920.544997198</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>383633.118855043</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>313979.507523135</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>440399.409388486</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>549802.94805102</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>603316.376051083</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>561933.965093327</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>554447.670134546</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>554152.906080568</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>526046.794636645</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>613811.066637611</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>646155.567584982</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>647174.693368069</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>663622.373763179</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>691772.001915824</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>89129.146</t>
+          <t>55388466776.1589</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48765.4</t>
+          <t>26528230295.0538</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>49780.583</t>
+          <t>29492591931.5091</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50512.35</t>
+          <t>18962014196.003</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>47655.703</t>
+          <t>24333265761.5855</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>48447.263</t>
+          <t>31840003839.2311</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50678.971</t>
+          <t>32791505531.1917</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>51745.589</t>
+          <t>35476514839.7568</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>53168.73</t>
+          <t>31493642300.296</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>53038.633</t>
+          <t>42016393817.1111</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>54153.754</t>
+          <t>42769058810.299</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>54841.327</t>
+          <t>44645606443.1299</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>55521.003</t>
+          <t>38570350040.573</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>55830.457</t>
+          <t>44788310852.2141</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>56633.551</t>
+          <t>37867177862.2366</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>56065.176</t>
+          <t>42082946055.1951</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>55898.407</t>
+          <t>49808338525.7353</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>56933.777</t>
+          <t>48854072062.8218</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>57958.028</t>
+          <t>51001773100.2002</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>55088.013</t>
+          <t>45962121697.003</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>66462.233</t>
+          <t>44893358697.9548</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>78217.401</t>
+          <t>48061757309.7068</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>77777.735</t>
+          <t>53238982380.0787</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>80198.855</t>
+          <t>58489142603.7658</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>80376.95</t>
+          <t>56468908244.1841</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>80575.582</t>
+          <t>61031525987.1709</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>80601.278</t>
+          <t>63520617835.11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>63979.516</t>
+          <t>-5757.43675625975</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12546.9</t>
+          <t>-19169.1500638412</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12965.635</t>
+          <t>-5469.62247488069</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13031.732</t>
+          <t>47265.0774580484</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>10644.773</t>
+          <t>33046.4774012231</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11519.299</t>
+          <t>14539.2593181954</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13495.613</t>
+          <t>10799.4089912935</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13935.695</t>
+          <t>10333.642845886</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14930.33</t>
+          <t>13156.2246546092</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>15963.491</t>
+          <t>29126.0273520171</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17258.712</t>
+          <t>22046.3502847814</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>17932.969</t>
+          <t>6593.88653221382</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>18992.347</t>
+          <t>10189.8315258476</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>20735.217</t>
+          <t>-2165.93075384292</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>21009.087</t>
+          <t>37518.5882574112</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>22212.254</t>
+          <t>31695.0935490726</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>23517.883</t>
+          <t>13061.3242568318</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>24545.701</t>
+          <t>35528.3681463563</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>24995.408</t>
+          <t>62534.7776512485</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>39652.84</t>
+          <t>73778.0048064649</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>47984.688</t>
+          <t>118310.70129381</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>55827.931</t>
+          <t>118084.928411161</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>55856.191</t>
+          <t>89262.4660088488</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>57382.663</t>
+          <t>84770.5316849744</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>57759.799</t>
+          <t>55774.8373103414</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>57516.397</t>
+          <t>64265.6820348502</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>57720.477</t>
+          <t>62702.6220828182</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>128018.605</t>
+          <t>-34819665762.5568</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>67417.198</t>
+          <t>-16801841085.2615</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>73608.69</t>
+          <t>-18054924548.9009</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>62454.673</t>
+          <t>-5860436594.66679</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>65100.428</t>
+          <t>-12335038043.8006</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>73633.134</t>
+          <t>-17888250873.5036</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>73893.491</t>
+          <t>-19293882174.4375</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77598.177</t>
+          <t>-21305846471.2424</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>73299.362</t>
+          <t>-18074434035.3245</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>89527.747</t>
+          <t>-23840867295.8301</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>93493.176</t>
+          <t>-24719587110.581</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>93688.608</t>
+          <t>-26125524013.4929</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>90355.466</t>
+          <t>-20935520672.1544</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>98700.988</t>
+          <t>-22490406409.8837</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>87506.358</t>
+          <t>-16885986622.5922</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>89846.238</t>
+          <t>-20972530371.9909</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>100399.176</t>
+          <t>-23025422151.395</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>95954.058</t>
+          <t>-22920883254.655</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>100889.499</t>
+          <t>-23883530312.453</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>97591.951</t>
+          <t>-21286040084.4925</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>110104.221</t>
+          <t>-20055844226.7749</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>121049.575</t>
+          <t>-20831675943.0167</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>129304.716</t>
+          <t>-24706585951.9067</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>138620.919</t>
+          <t>-27174659042.6541</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>135857.3</t>
+          <t>-26696277756.9879</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>141037.764</t>
+          <t>-29217907994.7565</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>147716.555</t>
+          <t>-31235064637.0034</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>202424.665653291</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>213112.115575458</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>225966.879633465</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>141807.3810095</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>191527.055732007</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>262997.875131859</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>249810.436748567</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>275976.425141903</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>275519.567115322</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>287856.18336402</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>343972.491573588</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>394658.97946972</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>395620.619567872</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>330242.545944111</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>312701.041845908</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>385836.71876814</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1.179</t>
+          <t>405076.745231424</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>457340.463400967</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>464131.092224047</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.264</t>
+          <t>389169.606820012</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>1.592</t>
+          <t>602485.772617131</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>566564.16235677</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>687369.046192802</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>632965.075777982</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1.922</t>
+          <t>624771.72811932</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>1.901</t>
+          <t>631474.677827976</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1.954</t>
+          <t>708261.362207906</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>46704.994</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>27513.917</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>27432.192</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>27271.47</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>25025.315</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>24877.721</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>26475.314</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>26718.98</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>27544.571</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>27622.393</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>28014.601</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>28182.226</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>28456.4</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>28432.318</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>29150.068</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>28627.209</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>29128.73</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>29539.268</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>29912.213</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>29491.684</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>32222.401</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>38909.961</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>38851.937</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>41233.621</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>41002.192</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>41045.377</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>40763.345</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>292051.965163977</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>312299.96371662</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>317076.715106288</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>209449.457402412</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>286003.549313443</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>383999.307018593</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>375396.756504618</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>406742.343743314</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>403235.255563521</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>407677.791841395</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>481168.427849887</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>555414.988545693</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>547949.309759866</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>459541.141479631</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>430766.415009101</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>537665.613323611</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>546574.924738766</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>613056.423719062</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>662092.897772865</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>653548.332290575</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>813759.382840172</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>827578.378985177</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>949151.561904739</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>836276.27258748</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>895043.435118942</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>915043.02714723</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>958738.095422895</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>39826.693</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>20991.032</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>21840.702</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>16630.501</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>17624.302</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>19344.039</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20246.446</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>20892.832</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>22062.189</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>23852.061</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>23901.394</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>27740.942</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>22196.979</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>23436.388</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>21285.957</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>20380.849</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>20876.142</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>23846.7</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>24125.873</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>22021.754</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>17743.26</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>22709.797</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>24381.239</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>20635.513</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>22820.013</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>22331.872</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>22152.736</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>60.64</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-40.23</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-40.64</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-21.64</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-39.6</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-40.45</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-33.34</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-33.3</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-32.33</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-33.07</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-27.79</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-35.36</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-14.44</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-11.53</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>8.99</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>12.65</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>80.06</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>170.44</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>145.83</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>129.09</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>178.08</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>153.11</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>157.55</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>160.56</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>51.294</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>28.315</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>29.668</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>33.904</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>17.231</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>12.035</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12.639</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>11.041</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>11.976</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>11.532</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>10.852</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>11.156</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>8.619</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>10.387</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>10.915</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>7.775</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>8.04</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>6.69</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>8.305</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>7.916</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>9.625</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>9.286</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>9.653</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>9.366</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>9.472</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>8.331</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>251790.202080117</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>289132.850795534</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>309697.950765104</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>215373.219948921</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>294823.129699171</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>386896.553132957</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>383884.68560689</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>419742.408755445</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>368749.344047157</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>385126.105797534</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>452209.999005311</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>484613.95480682</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>511382.230638293</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>424082.398092875</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>400990.04779973</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>524697.871378873</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>558880.66985431</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>604458.371134873</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>608071.356235563</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>722011.509659645</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>801185.641656376</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>821583.242634346</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>790698.779642774</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>934628.998985244</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>895241.748242012</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>914170.623568449</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>928719.335856653</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>63979515598.4278</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>12546899999.9982</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>12965635000.0012</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>13031731999.9842</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>10644773000.0072</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>11519299000.0118</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>13495613000.0174</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>13935694999.9791</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>14930329999.9935</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>15963491000.0049</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>17258711999.9949</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>17932968999.9945</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>18992347000.0068</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>20735216999.9864</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>21009086999.9898</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>22212254000.0247</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>23517882999.9935</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>24545700999.9974</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>24995408000.004</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>39652840230.6264</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>47984688372.7543</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>55827931409.3387</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>55856191457.3595</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>57382663432.8317</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>57759799329.0183</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>57516396599.2253</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>57720477029.7115</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>89129146463.853</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>48765399999.9985</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>49780583000.0033</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50512349999.9962</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>47655703000.0089</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>48447263000.0024</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50678971000.0163</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>51745588999.9909</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>53168730000.0079</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>53038633000.0129</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>54153753999.9919</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>54841326999.9967</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>55521002999.9991</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>55830456999.9893</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>56633550999.9937</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>56065176000.0134</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>55898407000.0023</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>56933776999.9972</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>57958028000.0101</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>55088012997.7372</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>66462233407.5278</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>78217401206.6199</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>77777734876.5221</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>80198855272.0631</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>80376950222.1345</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>80575581910.1064</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>80601277574.8873</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>46704994484.721</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>27513916710.5055</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>27432192315.9808</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>27271470368.8287</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>25025315286.4199</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>24877721075.604</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>26475314207.8841</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>26718979954.1648</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>27544570701.9999</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>27622393476.479</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>28014601382.4763</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>28182225726.8857</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>28456400329.4622</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>28432317522.4021</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>29150067695.4941</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>28627208693.9023</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>29128729850.3464</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>29539267695.7497</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>29912213002.5058</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>29491684051.1605</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>32222401240.6791</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>38909961488.087</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>38851937475.2029</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>41233621221.4173</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>41002191898.1997</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>41045376949.7922</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>40763345126.0177</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>37777168.9064571</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20470499.9999992</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>20857400.0000033</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>21150799.9999972</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20019799.9999997</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>20307900.0000006</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>21183999.9999969</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>21600500.0000037</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>22190999.9999962</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>22174000.0000074</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>22587000.0000039</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>22885199.9999998</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>23188199.9999982</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>23348400.0000014</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>23678699.9999989</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>23493099.9999942</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>23815599.9999985</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>24231599.9999966</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>24671399.9999932</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>23426143.3800846</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>28325408.3365928</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>33322823.0226519</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>33152447.2575494</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>34128999.9682418</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>34174077.3234212</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>34306606.8787629</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>34274098.4086232</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>27464935.1663897</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>12812699.9999981</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>13098999.9999991</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>13266099.9999943</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>12210500.0000008</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>12547399.9999959</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13382499.9999961</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>13681500.0000061</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14199499.9999999</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14430900.0000062</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>14916500.0000039</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>15207400.0000011</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>15581200.0000019</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>16014500.0000008</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>16247399.9999991</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>16441099.9999937</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>16957199.9999995</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>17384199.9999991</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>17702599.9999929</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>16978401.2111283</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>20640477.3032317</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>24036827.6346597</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>24111851.9507518</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>24771397.559498</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>24898785.5065045</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>24865880.3749196</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>24905112.6640106</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>89129146463.853</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>48765399999.9985</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>49780583000.0033</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>50512349999.9962</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>47655703000.0089</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>48447263000.0024</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50678971000.0163</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>51745588999.9909</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>53168730000.0079</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>53038633000.0129</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>54153753999.9919</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>54841326999.9967</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>55521002999.9991</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>55830456999.9893</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>56633550999.9937</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>56065176000.0134</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>55898407000.0023</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>56933776999.9972</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>57958028000.0101</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>55088012997.7372</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>66462233407.5278</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>78217401206.6199</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>77777734876.5221</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>80198855272.0631</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>80376950222.1345</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>80575581910.1064</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>80601277574.8873</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>63979515598.4278</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>12546899999.9982</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>12965635000.0012</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>13031731999.9842</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>10644773000.0072</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11519299000.0118</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>13495613000.0174</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>13935694999.9791</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>14930329999.9935</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>15963491000.0049</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>17258711999.9949</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>17932968999.9945</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>18992347000.0068</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>20735216999.9864</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>21009086999.9898</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>22212254000.0247</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>23517882999.9935</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>24545700999.9974</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>24995408000.004</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>39652840230.6264</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>47984688372.7543</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>55827931409.3387</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>55856191457.3595</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>57382663432.8317</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>57759799329.0183</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>57516396599.2253</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>57720477029.7115</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1134965.43546709</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1273905.00913908</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1331859.03003765</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>927002.064653267</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1269641.1815062</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1758611.33877191</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1674402.65153181</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1810339.60879575</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1706994.76438443</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1855304.39152482</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2229770.93222595</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2525543.36900993</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2628948.47986759</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2336095.86555555</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2117523.74710528</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2818254.91569721</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>3030940.89959078</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>3318473.09761543</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>3309690.6625741</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>3872393.27904267</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>4626216.57446518</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>4648763.71421275</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>4963824.13734091</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>5050895.90338274</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>5034999.51958596</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>5137553.31786546</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>5432938.49575895</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>316275.560538257</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>341426.001832835</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>349598.499617468</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>233316.21150129</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>317624.859034787</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>431535.20800052</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>418858.755094578</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>451278.21564484</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>447195.247601573</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>452048.178070333</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>534680.402334596</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>617255.402744607</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>612579.348697739</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>511527.183093146</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>488020.121485369</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>608399.331502583</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>623151.235772081</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>702299.028305716</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>747398.20656357</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>745547.378146038</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>934680.524813499</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>959464.59311781</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1098009.58184404</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>984578.054481153</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1038624.25527945</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>1062560.5206201</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1102227.30018749</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
